--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VCN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VDA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VDT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAW" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IRI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VCN_Success" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VDA_Success" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VDT_Success" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUI_Success" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUT_Success" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAW_Success" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IRI_Success" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -70,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -78,14 +78,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -456,306 +463,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VCN - Card Acquisition Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: Card Acquisition | Source: DDWV01.VISA_DR_CRD_DLY | Date Field: ISS_DT</t>
-        </is>
-      </c>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VCN</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(STS_CD, SRVC_ID)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ISS_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ISS_DT  AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t>ORGANIC SUCCESS (All Events)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ISS_DT  AS SUCCESS_DT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.ISS_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VCN'</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>
@@ -772,306 +912,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VDA - Card Acquisition Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: Card Acquisition | Source: DDWV01.VISA_DR_CRD_DLY | Date Field: ISS_DT</t>
-        </is>
-      </c>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VDA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(STS_CD, SRVC_ID)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ISS_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ISS_DT  AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t>ORGANIC SUCCESS (All Events)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ISS_DT  AS SUCCESS_DT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.ISS_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDA'</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>
@@ -1088,306 +1361,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VDT - Card Activation Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: Card Activation | Source: DDWV01.VISA_DR_CRD_DLY | Date Field: ACTV_DT</t>
-        </is>
-      </c>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VDT</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(STS_CD, SRVC_ID)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ACTV_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ACTV_DT  AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t>ORGANIC SUCCESS (All Events)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ACTV_DT  AS SUCCESS_DT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.ACTV_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDT'</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>
@@ -1404,306 +1810,439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VUI - Card Usage Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: Card Usage | Source: DDWV01.VISA_DR_CRD_DLY | Date Field: ACTV_DT</t>
-        </is>
-      </c>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VUI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(STS_CD, SRVC_ID)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ACTV_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ACTV_DT  AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t>ORGANIC SUCCESS (All Events)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ACTV_DT  AS SUCCESS_DT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.ACTV_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>
@@ -1720,376 +2259,513 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VUT - Wallet Provisioning Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: Wallet Provisioning | Source: DDWV05.CLNT_CRD_POS_LOG + DL_DECMAN.TOKEN_LIST | Date Field: TXN_DT</t>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_CRD_NO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VUT</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG + DL_DECMAN.TOKEN_LIST</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(TOKN_REQSTR_ID, TOKEN_WALLET_IND)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>TXN_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>ORGANIC SUCCESS (All Events)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        D.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        D.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        D.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VUT'</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>
@@ -2106,376 +2782,513 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VAW - Wallet Provisioning Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: Wallet Provisioning | Source: DDWV05.CLNT_CRD_POS_LOG + DL_DECMAN.TOKEN_LIST | Date Field: TXN_DT</t>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_CRD_NO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VAW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG + DL_DECMAN.TOKEN_LIST</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(TOKN_REQSTR_ID, TOKEN_WALLET_IND)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>TXN_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>ORGANIC SUCCESS (All Events)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        D.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        D.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        D.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VAW'</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>
@@ -2492,264 +3305,409 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IRI - International Money Transfer Success</t>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Metric: IMT Transaction | Source: DDWV01.EXT_CDS_CHNL_EVNT | Date Field: CAPTR_DT | Filter: ACTVY_TYP_CD = '031'</t>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.EXT_CDS_CHNL_EVNT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.EXT_CDS_CHNL_EVNT</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>AR_ID</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ORGANIC SUCCESS (All Events)</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.EXT_CDS_CHNL_EVNT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EVNT_AMT_CAD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PROC SQL;</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>IRI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CREATE TABLE work.organic_success AS</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.EXT_CDS_CHNL_EVNT</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(CHNL_TYP_CD, EVNT_CRNCY_CD, ACTVY_TYP_CD)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.EXT_CDS_CHNL_EVNT</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CAPTR_DT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT DISTINCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CAPTR_DT  AS SUCCESS_DT</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE ACTVY_TYP_CD = '031'        /* 031 = International Money Transfer */</t>
+          <t>ORGANIC SUCCESS (All Events)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>);</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DISCONNECT FROM EDW;</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>CREATE TABLE work.organic_success AS</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>QUIT;</t>
-        </is>
-      </c>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    SELECT DISTINCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CAPTR_DT  AS SUCCESS_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE ACTVY_TYP_CD = '031'        /* 031 = International Money Transfer */</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>CAMPAIGN SUCCESS (Tactic-Linked)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>PROC SQL;</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>CREATE TABLE work.campaign_success AS</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>SELECT * FROM CONNECTION TO EDW (</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    SELECT DISTINCT</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        A.CAPTR_DT           AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'          /* 031 = International Money Transfer */</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>);</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>DISCONNECT FROM EDW;</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>QUIT;</t>
         </is>

--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -14,6 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VUT_Success" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAW_Success" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IRI_Success" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="O2P_Success" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAT_Success" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDE_Success" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIS_Success" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAO_Success" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1240,6 +1245,1951 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(DI_DT_OPEN, IE_DT_OPEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>COALESCE(DI_DT_OPEN, IE_DT_OPEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        DI_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IE_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)   AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                  AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IDE) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        DI_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IE_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Treatmt_strt_dt,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IDE) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)   AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                  AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>dt_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (GIS) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Treatmt_strt_dt,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (GIS) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C90"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PLN_AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>TAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>dt_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        PLN_AR_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE PLN_AR_ID IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE PLN_AR_ID IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (TAO) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        PLN_AR_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Treatmt_strt_dt</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND PLN_AR_ID IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (TAO) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND PLN_AR_ID IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6194,4 +8144,2026 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C153"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.CR_APP_CLNT_RELTN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.CR_APP_PROD</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PROD_APP_ACCT_TR_NO || APP_ACCT_NO  (derived AR_ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>O2P</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.CR_APP_PROD</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(APPL_FOR_PROD_TYP, PROD_APP_STS_CD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.CR_APP_PROD</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PROD_APP_COMPL_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (O2P) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C131"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DG6V01.ARNGMNT_OWN_HIST</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DG6V01.ARNGMNT_HIST</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>RAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DG6V01.ARNGMNT_HIST</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(INVSTMT_PLN_TYPE, OP_CLS_STS, MIF_SRVC_ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DG6V01.ARNGMNT_HIST</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DT_OPENED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        OWN.CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.AR_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        OWN.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (RAT) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        HIST.AR_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (RAT) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>PROC SQL;</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>SELECT * FROM CONNECTION TO EDW (</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>DISCONNECT FROM EDW;</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>QUIT;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -638,21 +638,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -749,14 +749,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -770,21 +770,21 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -888,14 +888,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -909,21 +909,21 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -1062,14 +1062,14 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -1083,21 +1083,21 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -1229,14 +1229,14 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -1410,21 +1410,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -1514,14 +1514,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -1535,21 +1535,21 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -1632,14 +1632,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -1653,21 +1653,21 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -1771,14 +1771,14 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -1792,21 +1792,21 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -1896,14 +1896,14 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2073,21 +2073,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -2163,14 +2163,14 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2184,21 +2184,21 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -2281,14 +2281,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2302,21 +2302,21 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -2406,14 +2406,14 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2427,21 +2427,21 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -2531,14 +2531,14 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2716,21 +2716,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -2806,14 +2806,14 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2827,21 +2827,21 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -2924,14 +2924,14 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -2945,21 +2945,21 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -3049,14 +3049,14 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -3070,21 +3070,21 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -3174,14 +3174,14 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -3359,21 +3359,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -3470,14 +3470,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -3491,21 +3491,21 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -3609,14 +3609,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -3630,21 +3630,21 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -3783,14 +3783,14 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -3804,21 +3804,21 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -3950,14 +3950,14 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -4135,21 +4135,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -4253,14 +4253,14 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -4274,21 +4274,21 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -4399,14 +4399,14 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -4420,21 +4420,21 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -4580,14 +4580,14 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -4601,21 +4601,21 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -4754,14 +4754,14 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -4939,21 +4939,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -5050,14 +5050,14 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -5071,21 +5071,21 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -5189,14 +5189,14 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -5210,21 +5210,21 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -5363,14 +5363,14 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -5384,21 +5384,21 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -5530,14 +5530,14 @@
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -5719,21 +5719,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -5865,14 +5865,14 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -5886,21 +5886,21 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -6046,14 +6046,14 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -6067,21 +6067,21 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -6248,14 +6248,14 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -6269,21 +6269,21 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -6457,14 +6457,14 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -6646,21 +6646,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -6792,14 +6792,14 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -6813,21 +6813,21 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -6973,14 +6973,14 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -6994,21 +6994,21 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -7175,14 +7175,14 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -7196,21 +7196,21 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -7384,14 +7384,14 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -7581,21 +7581,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -7685,14 +7685,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -7706,21 +7706,21 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -7810,14 +7810,14 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -7831,21 +7831,21 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -7977,14 +7977,14 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -7998,21 +7998,21 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -8130,14 +8130,14 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -8319,21 +8319,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -8507,14 +8507,14 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -8528,21 +8528,21 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -8723,14 +8723,14 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -8744,21 +8744,21 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -8974,14 +8974,14 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -8995,21 +8995,21 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -9218,14 +9218,14 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -9407,21 +9407,21 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -9553,14 +9553,14 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -9574,21 +9574,21 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -9713,14 +9713,14 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -9734,21 +9734,21 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -9943,14 +9943,14 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
@@ -9964,21 +9964,21 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>PROC SQL;</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>CONNECT TO TERADATA AS EDW (MODE=TERADATA);</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>SELECT * FROM CONNECTION TO EDW (</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
@@ -10152,14 +10152,14 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>DISCONNECT FROM EDW;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>QUIT;</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>

--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -732,509 +732,537 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND ISS_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY ISS_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-    </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM ISS_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM ISS_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM ISS_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)    AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM ISS_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                   AS total_events</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)    AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+          <t xml:space="preserve">        COUNT(*)                   AS total_events</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (VCN) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.ISS_DT            AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.STS_CD,</t>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TACTIC_ID,</t>
+          <t xml:space="preserve">        A.ISS_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        A.STS_CD,</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
+          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VCN'</t>
+          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY A.ISS_DT DESC</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VCN'</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY A.ISS_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VCN) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VCN) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ISS_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ISS_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)    AS unique_clients,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                     AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ISS_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ISS_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)    AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">        COUNT(*)                     AS total_events</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VCN'</t>
+          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VCN'</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -1246,6 +1274,701 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(DI_DT_OPEN, IE_DT_OPEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>COALESCE(DI_DT_OPEN, IE_DT_OPEN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        DI_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IE_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)   AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                  AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IDE) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        DI_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IE_DT_OPEN,</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Control,</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Treatmt_strt_dt,</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IDE) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)   AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                  AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND Success = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1284,7 +2007,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1320,7 +2043,7 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IDE</t>
+          <t>GIS</t>
         </is>
       </c>
     </row>
@@ -1341,14 +2064,10 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>JSON(DI_DT_OPEN, IE_DT_OPEN)</t>
-        </is>
-      </c>
+          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1358,12 +2077,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>dl_mr_prod.NBO_IDE_Acquisition</t>
+          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(DI_DT_OPEN, IE_DT_OPEN)</t>
+          <t>dt_open</t>
         </is>
       </c>
     </row>
@@ -1448,160 +2167,160 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        DI_DT_OPEN,</t>
+          <t xml:space="preserve">        Control,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        IE_DT_OPEN,</t>
+          <t xml:space="preserve">        Success</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Control,</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Success</t>
+          <t xml:space="preserve">    WHERE Success = 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE Success = 1</t>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>ORGANIC — Summary (by year-month)</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
+      <c r="A37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)   AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                  AS total_events</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+          <t xml:space="preserve">    WHERE Success = 1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE Success = 1</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
@@ -1646,7 +2365,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>CAMPAIGN (IDE) — Sample (10 rows)</t>
+          <t>CAMPAIGN (GIS) — Sample (10 rows)</t>
         </is>
       </c>
     </row>
@@ -1691,181 +2410,181 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        DI_DT_OPEN,</t>
+          <t xml:space="preserve">        Control,</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        IE_DT_OPEN,</t>
+          <t xml:space="preserve">        Treatmt_strt_dt,</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Control,</t>
+          <t xml:space="preserve">        Success</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Treatmt_strt_dt,</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Success</t>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+          <t xml:space="preserve">      AND Success = 1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND Success = 1</t>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
-        </is>
-      </c>
+      <c r="A70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (GIS) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (IDE) — Summary (by year-month)</t>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
+      <c r="A79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)   AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                  AS total_events</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_IDE_Acquisition</t>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+          <t xml:space="preserve">      AND Success = 1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND Success = 1</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
@@ -1902,641 +2621,6 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C90"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Target Column</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source table</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>source column/logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>clnt_no</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>CLNT_NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>acct_no</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>event_mnemonic_cd</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>GIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>event_type_cd</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>event_attributes</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>event_dt</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>dt_open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>snap_dt</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>&lt;GENERATED&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>job_id</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>&lt;GENERATED&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Query:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ORGANIC — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Control,</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE Success = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE Success = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (GIS) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Control,</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Treatmt_strt_dt,</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE Control = 'Action'</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND Success = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (GIS) — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_GIC_Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE Control = 'Action'</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND Success = 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -2553,7 +2637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2789,397 +2873,425 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY dt_open DESC</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-    </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE PLN_AR_ID IS NOT NULL</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    WHERE PLN_AR_ID IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (TAO) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        PLN_AR_ID,</t>
+          <t xml:space="preserve">        CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Control,</t>
+          <t xml:space="preserve">        dt_open               AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Treatmt_strt_dt</t>
+          <t xml:space="preserve">        PLN_AR_ID,</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+          <t xml:space="preserve">        Control,</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+          <t xml:space="preserve">        Treatmt_strt_dt</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND PLN_AR_ID IS NOT NULL</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr"/>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND PLN_AR_ID IS NOT NULL</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY dt_open DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (TAO) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (TAO) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
-        </is>
-      </c>
+      <c r="A79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM dt_open)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM dt_open) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE Control = 'Action'</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND PLN_AR_ID IS NOT NULL</t>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    FROM dl_mr_prod.NBO_TAO_Acquisition</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">    WHERE Control = 'Action'</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr"/>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND PLN_AR_ID IS NOT NULL</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND dt_open &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -3191,782 +3303,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Target Column</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source table</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>source column/logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>clnt_no</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>CLNT_NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>acct_no</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>event_mnemonic_cd</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>VDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>event_type_cd</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>event_attributes</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>JSON(STS_CD, SRVC_ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>event_dt</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ISS_DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>snap_dt</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>&lt;GENERATED&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>job_id</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>&lt;GENERATED&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Query:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>ORGANIC — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ISS_DT        AS SUCCESS_DT,</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        STS_CD,</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SRVC_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY ISS_DT DESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM ISS_DT)  AS yr,</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM ISS_DT) AS mo,</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)    AS unique_clients,</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(*)                   AS total_events</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VDA) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.ISS_DT            AS SUCCESS_DT,</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.STS_CD,</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        B.TACTIC_ID,</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        B.TREATMT_END_DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY A.ISS_DT DESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VDA) — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ISS_DT)  AS yr,</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ISS_DT) AS mo,</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)    AS unique_clients,</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(*)                     AS total_events</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDA'</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4045,7 +3381,7 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>VDA</t>
         </is>
       </c>
     </row>
@@ -4088,7 +3424,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ACTV_DT</t>
+          <t>ISS_DT</t>
         </is>
       </c>
     </row>
@@ -4173,7 +3509,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ACTV_DT       AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        ISS_DT        AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
@@ -4222,21 +3558,21 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND ACTV_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY ACTV_DT DESC</t>
+          <t xml:space="preserve">    ORDER BY ISS_DT DESC</t>
         </is>
       </c>
     </row>
@@ -4305,28 +3641,28 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM ACTV_DT)  AS yr,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM ISS_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM ACTV_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM ISS_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)    AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+          <t xml:space="preserve">        COUNT(*)                   AS total_events</t>
         </is>
       </c>
     </row>
@@ -4361,14 +3697,14 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND ACTV_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
@@ -4413,7 +3749,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>CAMPAIGN (VDT) — Sample (10 rows)</t>
+          <t>CAMPAIGN (VDA) — Sample (10 rows)</t>
         </is>
       </c>
     </row>
@@ -4458,7 +3794,7 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.ACTV_DT           AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        A.ISS_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
@@ -4535,35 +3871,35 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ACTV_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDA'</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDT'</t>
+          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND A.ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY A.ACTV_DT DESC</t>
+          <t xml:space="preserve">    ORDER BY A.ISS_DT DESC</t>
         </is>
       </c>
     </row>
@@ -4594,7 +3930,7 @@
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>CAMPAIGN (VDT) — Summary (by year-month)</t>
+          <t>CAMPAIGN (VDA) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
@@ -4632,28 +3968,28 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ACTV_DT)  AS yr,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ISS_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ACTV_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ISS_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)     AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)    AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
+          <t xml:space="preserve">        COUNT(*)                     AS total_events</t>
         </is>
       </c>
     </row>
@@ -4702,28 +4038,28 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ACTV_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDA'</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDT'</t>
+          <t xml:space="preserve">      AND A.ISS_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND A.ISS_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
@@ -4760,6 +4096,838 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>source table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source column/logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>clnt_no</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>acct_no</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>event_mnemonic_cd</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>event_type_cd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>event_attributes</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSON(STS_CD, SRVC_ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>event_dt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ACTV_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>snap_dt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>&lt;GENERATED&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Query:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>ORGANIC — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ACTV_DT       AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        STS_CD,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SRVC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ACTV_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ACTV_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY ACTV_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM ACTV_DT)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM ACTV_DT) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ACTV_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND ACTV_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VDT) — Sample (10 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT TOP 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        A.ACTV_DT           AS SUCCESS_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        A.STS_CD,</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        B.TACTIC_ID,</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        B.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ACTV_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ACTV_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY A.ACTV_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VDT) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>proc sql;</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>select * from connection to teradata (</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SELECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ACTV_DT)  AS yr,</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ACTV_DT) AS mo,</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)     AS unique_clients,</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ACTV_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VDT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.ACTV_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -4776,7 +4944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4809,12 +4977,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CLNT_NO</t>
+          <t>CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER)</t>
         </is>
       </c>
     </row>
@@ -4826,10 +4994,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CLNT_CRD_NO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4837,8 +5009,16 @@
           <t>amount</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>AMT1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4870,12 +5050,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>JSON(STS_CD, SRVC_ID)</t>
+          <t>JSON(TXN_TP, MSG_TP, SRVC_CD)</t>
         </is>
       </c>
     </row>
@@ -4887,12 +5067,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DDWV01.VISA_DR_CRD_DLY</t>
+          <t>DDWV05.CLNT_CRD_POS_LOG</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ACTV_DT</t>
+          <t>TXN_DT</t>
         </is>
       </c>
     </row>
@@ -4970,572 +5150,621 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        CLNT_NO,</t>
+          <t xml:space="preserve">        CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ACTV_DT       AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        TXN_DT            AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        STS_CD,</t>
+          <t xml:space="preserve">        AMT1,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SRVC_ID</t>
+          <t xml:space="preserve">        TXN_TP,</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+          <t xml:space="preserve">        MSG_TP,</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">        SRVC_CD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">    WHERE AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">      AND SUBSTR(CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY ACTV_DT DESC</t>
+          <t xml:space="preserve">      AND SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND TXN_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY TXN_DT DESC</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM ACTV_DT)  AS yr,</t>
-        </is>
-      </c>
+      <c r="A41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM ACTV_DT) AS mo,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)     AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">                                    AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SRVC_ID = 36</t>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">        SUM(AMT1)                   AS total_amount</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    WHERE AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND SUBSTR(CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRVC_CD = 36</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VUI) — Sample (10 rows)</t>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VUI) — Sample (10 rows)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.ACTV_DT           AS SUCCESS_DT,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.STS_CD,</t>
-        </is>
-      </c>
+      <c r="A66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TACTIC_ID,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        A.TXN_DT             AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
+          <t xml:space="preserve">        A.AMT1,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        A.TXN_TP,</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
+          <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG        AS A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER) = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">    WHERE A.AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY A.ACTV_DT DESC</t>
+          <t xml:space="preserve">      AND SUBSTR(A.CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.SRVC_CD = 36</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND A.TXN_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">      AND A.TXN_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY A.TXN_DT DESC</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VUI) — Summary (by year-month)</t>
-        </is>
-      </c>
+      <c r="A85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
+          <t>quit;</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VUI) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.ACTV_DT)  AS yr,</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.ACTV_DT) AS mo,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)     AS unique_clients,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
-        </is>
-      </c>
+      <c r="A94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.VISA_DR_CRD_DLY        AS A</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.STS_CD IN ('06','08')</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SRVC_ID = 36</t>
+          <t xml:space="preserve">                                      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ISS_DT IS NOT NULL</t>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SNAP_DT = (SELECT MAX(SNAP_DT) FROM DDWV01.VISA_DR_CRD_DLY WHERE SNAP_DT &gt;= CURRENT_DATE - 7)</t>
+          <t xml:space="preserve">        SUM(A.AMT1)                   AS total_amount</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG        AS A</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.ACTV_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER) = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">    WHERE A.AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SUBSTR(A.CLNT_CRD_NO, 1, 5) = '45190'</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.TXN_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.TXN_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -5552,7 +5781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5848,621 +6077,649 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY B.TXN_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
-    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                      AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
+          <t xml:space="preserve">                                      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
+          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
+          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
+          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (VUT) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.TACTIC_ID,</t>
+          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.TREATMT_END_DT</t>
+          <t xml:space="preserve">        D.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+          <t xml:space="preserve">        D.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
+          <t xml:space="preserve">        D.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
+          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
+          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VUT'</t>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY B.TXN_DT DESC</t>
+          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VUT'</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY B.TXN_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VUT) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VUT) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                      AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
+          <t xml:space="preserve">                                      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
+          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
+          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VUT'</t>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VUT'</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -6479,7 +6736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6775,621 +7032,649 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY B.TXN_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
-    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                      AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
+          <t xml:space="preserve">                                      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
+          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
+          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
+          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (VAW) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr"/>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.TACTIC_ID,</t>
+          <t xml:space="preserve">        CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        B.TXN_DT                                        AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.TREATMT_END_DT</t>
+          <t xml:space="preserve">        D.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+          <t xml:space="preserve">        D.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
+          <t xml:space="preserve">        D.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
+          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
+          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VAW'</t>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY B.TXN_DT DESC</t>
+          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VAW'</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY B.TXN_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VAW) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VAW) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                      AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM B.TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM B.TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
+          <t xml:space="preserve">                                      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG  AS B</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
+          <t xml:space="preserve">    INNER JOIN DL_DECMAN.TOKEN_LIST AS C</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
+          <t xml:space="preserve">        ON B.TOKN_REQSTR_ID = C.TOKEN_ID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS D</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(B.CLNT_CRD_NO, 7, 9) AS INTEGER) = D.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
+          <t xml:space="preserve">    WHERE B.AMT1 = 0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.CLNT_CRD_NO, 1, 5)  = '45190'</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND SUBSTR(B.VISA_DR_CRD_NO, 1, 5) = '45199'</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TOKN_REQSTR_ID, 1, 1) &gt; '0'</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VAW'</t>
+          <t xml:space="preserve">      AND B.POS_ENTR_MODE_CD_NON_EMV = '000'</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND B.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND C.TOKEN_WALLET_IND = 'Y'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND SUBSTR(D.TACTIC_ID, 8, 3) = 'VAW'</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.TXN_DT BETWEEN D.TREATMT_STRT_DT AND D.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND B.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -7406,7 +7691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7668,474 +7953,502 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND CAPTR_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY CAPTR_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr"/>
-    </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM CAPTR_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM CAPTR_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM CAPTR_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)      AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM CAPTR_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT EVNT_ID)      AS unique_transactions,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SUM(EVNT_AMT_CAD)            AS total_amt_cad</t>
+          <t xml:space="preserve">        COUNT(DISTINCT EVNT_ID)      AS unique_transactions,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT</t>
+          <t xml:space="preserve">        SUM(EVNT_AMT_CAD)            AS total_amt_cad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE ACTVY_TYP_CD = '031'</t>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    WHERE ACTVY_TYP_CD = '031'</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND CAPTR_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (IRI) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr"/>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.CAPTR_DT           AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.EVNT_ID,</t>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.EVNT_AMT_CAD,</t>
+          <t xml:space="preserve">        A.CAPTR_DT           AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.CHNL_TYP_CD,</t>
+          <t xml:space="preserve">        A.EVNT_ID,</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TACTIC_ID,</t>
+          <t xml:space="preserve">        A.EVNT_AMT_CAD,</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        A.CHNL_TYP_CD,</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
+          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY A.CAPTR_DT DESC</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.CAPTR_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY A.CAPTR_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (IRI) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IRI) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.CAPTR_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.CAPTR_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)      AS unique_clients,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.EVNT_ID)      AS unique_transactions,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.CAPTR_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SUM(A.EVNT_AMT_CAD)            AS total_amt_cad</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.CAPTR_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.EVNT_ID)      AS unique_transactions,</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">        SUM(A.EVNT_AMT_CAD)            AS total_amt_cad</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr"/>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.CAPTR_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -8152,7 +8465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8490,740 +8803,768 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr"/>
-    </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr"/>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (O2P) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
+          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TACTIC_ID,</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr"/>
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -9240,7 +9581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9536,628 +9877,656 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr"/>
-    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
+          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr"/>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (RAT) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr"/>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        T.CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
+          <t xml:space="preserve">        T.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
+          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.AR_ID,</t>
+          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TACTIC_ID,</t>
+          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        HIST.AR_ID,</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (RAT) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (RAT) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
-        </is>
-      </c>
+      <c r="A108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr"/>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>

--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -8465,7 +8465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8719,7 +8719,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
@@ -8782,789 +8782,817 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr"/>
-    </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr"/>
-    </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (O2P) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr"/>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A88" s="5" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
+          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TACTIC_ID,</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr"/>
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC   = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('OP','CR','AP')</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr"/>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -9581,7 +9609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9877,656 +9905,670 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND OWN.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr"/>
-    </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr"/>
-    </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
+          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND OWN.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (RAT) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        T.CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
+          <t xml:space="preserve">        T.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
+          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.AR_ID,</t>
+          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TACTIC_ID,</t>
+          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        HIST.AR_ID,</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>CAMPAIGN (RAT) — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr"/>
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
-        </is>
-      </c>
+      <c r="A110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr"/>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>

--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -8465,7 +8465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8782,817 +8782,943 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
+          <t xml:space="preserve">    JOIN DG6V01.ARNGMNT_OWN_HIST        AS E</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = E.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">        AND E.MIF_SRVC_ID IN (4)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">        AND E.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr"/>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>ORGANIC — Summary (by year-month)</t>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
-        </is>
-      </c>
+      <c r="A56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">    FROM DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">    JOIN DG6V01.ARNGMNT_OWN_HIST        AS E</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = E.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">        AND E.MIF_SRVC_ID IN (4)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND E.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    WHERE D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (O2P) — Sample (10 rows)</t>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
+      <c r="A86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr"/>
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (O2P) — Sample (10 rows)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TACTIC_ID,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        T.TREATMT_END_DT</t>
-        </is>
-      </c>
+      <c r="A96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+          <t xml:space="preserve">        D.PROD_APP_COMPL_DT   AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP,</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t xml:space="preserve">        D.PROD_APP_STS_CD,</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr"/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DG6V01.ARNGMNT_OWN_HIST        AS E</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = E.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">        AND E.MIF_SRVC_ID IN (4)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">        AND E.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr"/>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
+          <t xml:space="preserve">    ORDER BY D.PROD_APP_COMPL_DT DESC</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
-        </is>
-      </c>
+      <c r="A132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (O2P) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
-        </is>
-      </c>
+      <c r="A141" s="5" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM D.PROD_APP_COMPL_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM D.PROD_APP_COMPL_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)                AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
+          <t xml:space="preserve">        COUNT(*)                                 AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
+          <t xml:space="preserve">        D.APPL_FOR_PROD_TYP</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST   AS T</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_RELTN        AS A</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = A.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
+          <t xml:space="preserve">    JOIN DDWV01.OVRL_CR_APP              AS B</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+          <t xml:space="preserve">        ON B.CR_APP_ID  = A.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        AND B.SYS_SRC_ID = A.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_CLNT_PROD_RELTN   AS C</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        ON A.CR_APP_ID          = C.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+          <t xml:space="preserve">        AND A.CR_APP_CLNT_SEQ_NO = C.CR_APP_CLNT_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">        AND A.SYS_SRC_ID        = C.SYS_SRC_ID</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr"/>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DDWV01.CR_APP_PROD              AS D</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">        ON C.CR_APP_ID          = D.CR_APP_ID</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">        AND C.CR_APP_PROD_SEQ_NO = D.CR_APP_PROD_SEQ_NO</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND C.SYS_SRC_ID        = D.SYS_SRC_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    JOIN DG6V01.ARNGMNT_OWN_HIST        AS E</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON A.CLNT_NO = E.CLNT_NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND E.MIF_SRVC_ID IN (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND E.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'O2P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.APPL_FOR_PROD_TYP IN ('40','41','43')</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND B.APP_TYP = 'P'</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_STS_CD IN (32,37,45,47,51,56,62)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_DT BETWEEN T.TREATMT_STRT_DT AND T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND D.PROD_APP_COMPL_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2, D.APPL_FOR_PROD_TYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -9609,7 +9735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9891,684 +10017,796 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">    INNER JOIN DDWV01.AR_BAL_DLY        AS BAL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">        ON HIST.AR_ID = BAL.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND OWN.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
+          <t xml:space="preserve">        AND BAL.SNAP_DT = OWN.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        AND BAL.SRVC_ID IN (11, 16, 37, 13, 14, 19)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr"/>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND OWN.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>ORGANIC — Summary (by year-month)</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>ORGANIC — Summary (by year-month)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
-        </is>
-      </c>
+      <c r="A50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">        COUNT(DISTINCT OWN.CLNT_NO)        AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">    FROM DG6V01.ARNGMNT_OWN_HIST   AS OWN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST  AS HIST</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND OWN.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    INNER JOIN DDWV01.AR_BAL_DLY        AS BAL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">        ON HIST.AR_ID = BAL.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND BAL.SNAP_DT = OWN.MTH_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">        AND BAL.SRVC_ID IN (11, 16, 37, 13, 14, 19)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    WHERE HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND OWN.MTH_END_DT = (SELECT MAX(MTH_END_DT) FROM DG6V01.ARNGMNT_OWN_HIST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (RAT) — Sample (10 rows)</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
+      <c r="A72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr"/>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        T.CLNT_NO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (RAT) — Sample (10 rows)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        HIST.AR_ID,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TACTIC_ID,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
-        </is>
-      </c>
+      <c r="A82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        T.TREATMT_END_DT</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
+          <t xml:space="preserve">        T.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+          <t xml:space="preserve">        HIST.DT_OPENED         AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+          <t xml:space="preserve">        HIST.INVSTMT_PLN_TYPE,</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        HIST.OP_CLS_STS,</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+          <t xml:space="preserve">        HIST.AR_ID,</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+          <t xml:space="preserve">        T.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+          <t xml:space="preserve">        T.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">        T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    INNER JOIN DDWV01.AR_BAL_DLY        AS BAL</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">        ON HIST.AR_ID = BAL.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">        AND BAL.SNAP_DT = OWN.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND BAL.SRVC_ID IN (11, 16, 37, 13, 14, 19)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (RAT) — Summary (by year-month)</t>
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr"/>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
+          <t xml:space="preserve">    ORDER BY HIST.DT_OPENED DESC</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
-        </is>
-      </c>
+      <c r="A113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (RAT) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
-        </is>
-      </c>
+      <c r="A122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM HIST.DT_OPENED)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM HIST.DT_OPENED) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+          <t xml:space="preserve">        COUNT(DISTINCT T.CLNT_NO)          AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+          <t xml:space="preserve">        COUNT(*)                           AS total_events</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+          <t xml:space="preserve">    FROM DG6V01.TACTIC_EVNT_IP_AR_HIST AS T</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_OWN_HIST  AS OWN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+          <t xml:space="preserve">        ON T.CLNT_NO = OWN.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT = ADD_MONTHS(T.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">            - (EXTRACT(DAY FROM T.TREATMT_END_DT)) + 1, 1) - 1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.ARNGMNT_HIST       AS HIST</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr"/>
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON OWN.MIF_ACCT_NO  = HIST.MIF_ACCT_NO</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">        AND OWN.MIF_SRVC_ID  = HIST.MIF_SRVC_ID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">        AND OWN.AR_ID        = HIST.AR_ID</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND OWN.MTH_END_DT   = HIST.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    INNER JOIN DDWV01.AR_BAL_DLY        AS BAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ON HIST.AR_ID = BAL.AR_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND BAL.SNAP_DT = OWN.MTH_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        AND BAL.SRVC_ID IN (11, 16, 37, 13, 14, 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE SUBSTR(T.TACTIC_ID, 8, 3) = 'RAT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.OP_CLS_STS = 'O'</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.INVSTMT_PLN_TYPE IN (8)    /* 8 = RESP */</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= T.TREATMT_STRT_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &lt;= T.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND HIST.DT_OPENED &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>

--- a/metadata/success_queries.xlsx
+++ b/metadata/success_queries.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COALESCE(DI_DT_OPEN, IE_DT_OPEN)</t>
+          <t>CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
@@ -1525,14 +1525,14 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
+          <t xml:space="preserve">    ORDER BY 2 DESC</t>
         </is>
       </c>
     </row>
@@ -1601,14 +1601,14 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END) AS mo,</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COALESCE(DI_DT_OPEN, IE_DT_OPEN) AS SUCCESS_DT,</t>
+          <t xml:space="preserve">        CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
@@ -1796,14 +1796,14 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY COALESCE(DI_DT_OPEN, IE_DT_OPEN) DESC</t>
+          <t xml:space="preserve">    ORDER BY 2 DESC</t>
         </is>
       </c>
     </row>
@@ -1872,14 +1872,14 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN))  AS yr,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM COALESCE(DI_DT_OPEN, IE_DT_OPEN)) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END) AS mo,</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND COALESCE(DI_DT_OPEN, IE_DT_OPEN) &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND CASE WHEN DI_DT_OPEN IS NULL THEN IE_DT_OPEN WHEN IE_DT_OPEN IS NULL THEN DI_DT_OPEN WHEN DI_DT_OPEN = IE_DT_OPEN THEN DI_DT_OPEN ELSE NULL END &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5206,565 +5206,593 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(CLNT_CRD_NO, 1, 5) = '45190'</t>
+          <t xml:space="preserve">      AND TXN_TP IN (10, 13)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND SUBSTR(CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND TXN_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">      AND TXN_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">    ORDER BY TXN_DT DESC</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>);</t>
-        </is>
-      </c>
+      <c r="A33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
-        </is>
-      </c>
+      <c r="A42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM TXN_DT)  AS yr,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM TXN_DT) AS mo,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                    AS unique_clients,</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                    AS total_events,</t>
+          <t xml:space="preserve">                                    AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SUM(AMT1)                   AS total_amount</t>
+          <t xml:space="preserve">        COUNT(*)                    AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG</t>
+          <t xml:space="preserve">        SUM(AMT1)                   AS total_amount</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE AMT1 &gt; 0</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(CLNT_CRD_NO, 1, 5) = '45190'</t>
+          <t xml:space="preserve">    WHERE AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SRVC_CD = 36</t>
+          <t xml:space="preserve">      AND TXN_TP IN (10, 13)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND TXN_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND SUBSTR(CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>CAMPAIGN (VUI) — Sample (10 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr"/>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
-        </is>
-      </c>
+      <c r="A68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.TXN_DT             AS SUCCESS_DT,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.AMT1,</t>
+          <t xml:space="preserve">        CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER)  AS CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.TXN_TP,</t>
+          <t xml:space="preserve">        A.TXN_DT             AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TACTIC_ID,</t>
+          <t xml:space="preserve">        A.AMT1,</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        A.TXN_TP,</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG        AS A</t>
+          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER) = B.CLNT_NO</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG        AS A</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.AMT1 &gt; 0</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(A.CLNT_CRD_NO, 1, 5) = '45190'</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER) = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SRVC_CD = 36</t>
+          <t xml:space="preserve">    WHERE A.AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
+          <t xml:space="preserve">      AND A.TXN_TP IN (10, 13)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.TXN_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND SUBSTR(A.CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.TXN_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND A.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY A.TXN_DT DESC</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.TXN_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">    ORDER BY A.TXN_DT DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>disconnect from teradata;</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>quit;</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (VUI) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
+          <t>quit;</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (VUI) — Summary (by year-month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
           <t>proc sql;</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.TXN_DT)  AS yr,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.TXN_DT) AS mo,</t>
-        </is>
-      </c>
+      <c r="A97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                      AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.TXN_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(*)                      AS total_events,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.TXN_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SUM(A.AMT1)                   AS total_amount</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER))</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG        AS A</t>
+          <t xml:space="preserve">                                      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        COUNT(*)                      AS total_events,</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER) = B.CLNT_NO</t>
+          <t xml:space="preserve">        SUM(A.AMT1)                   AS total_amount</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.AMT1 &gt; 0</t>
+          <t xml:space="preserve">    FROM DDWV05.CLNT_CRD_POS_LOG        AS A</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(A.CLNT_CRD_NO, 1, 5) = '45190'</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.SRVC_CD = 36</t>
+          <t xml:space="preserve">        ON CAST(SUBSTR(A.CLNT_CRD_NO, 7, 9) AS INTEGER) = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
+          <t xml:space="preserve">    WHERE A.AMT1 &gt; 0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.TXN_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">      AND A.TXN_TP IN (10, 13)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.TXN_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND SUBSTR(A.CLNT_CRD_NO, 1, 5) = '45190'</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">      AND A.SRVC_CD = 36</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'VUI'</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.TXN_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.TXN_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
@@ -7691,7 +7719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7802,7 +7830,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>JSON(CHNL_TYP_CD, EVNT_CRNCY_CD, ACTVY_TYP_CD)</t>
+          <t>JSON(CHNL_TYP_CD, EVNT_CRNCY_CD, ACTVY_TYP_CD, SRC_DTA_STORE_CD)</t>
         </is>
       </c>
     </row>
@@ -7953,502 +7981,558 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND CAPTR_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">      AND CHNL_TYP_CD IN ('021','034')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY CAPTR_DT DESC</t>
+          <t xml:space="preserve">      AND SRC_DTA_STORE_CD IN ('139','140')</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND CAPTR_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">    ORDER BY CAPTR_DT DESC</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>disconnect from teradata;</t>
-        </is>
-      </c>
+      <c r="A32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>quit;</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>ORGANIC — Summary (by year-month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr"/>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>%connectsql</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM CAPTR_DT)  AS yr,</t>
-        </is>
-      </c>
+      <c r="A41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM CAPTR_DT) AS mo,</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)      AS unique_clients,</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM CAPTR_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT EVNT_ID)      AS unique_transactions,</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM CAPTR_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SUM(EVNT_AMT_CAD)            AS total_amt_cad</t>
+          <t xml:space="preserve">        COUNT(DISTINCT CLNT_NO)      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT</t>
+          <t xml:space="preserve">        COUNT(DISTINCT EVNT_ID)      AS unique_transactions,</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE ACTVY_TYP_CD = '031'</t>
+          <t xml:space="preserve">        SUM(EVNT_AMT_CAD)            AS total_amt_cad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND CAPTR_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    WHERE ACTVY_TYP_CD = '031'</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">      AND CHNL_TYP_CD IN ('021','034')</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SRC_DTA_STORE_CD IN ('139','140')</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND CAPTR_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (IRI) — Sample (10 rows)</t>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>%connectsql</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>select * from connection to teradata (</t>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr"/>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IRI) — Sample (10 rows)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SELECT TOP 10</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.CLNT_NO,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.CAPTR_DT           AS SUCCESS_DT,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        A.EVNT_ID,</t>
-        </is>
-      </c>
+      <c r="A65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.EVNT_AMT_CAD,</t>
+          <t xml:space="preserve">    SELECT TOP 10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        A.CHNL_TYP_CD,</t>
+          <t xml:space="preserve">        A.CLNT_NO,</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TACTIC_ID,</t>
+          <t xml:space="preserve">        A.CAPTR_DT           AS SUCCESS_DT,</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
+          <t xml:space="preserve">        A.EVNT_ID,</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        A.EVNT_AMT_CAD,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
+          <t xml:space="preserve">        A.CHNL_TYP_CD,</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        B.TACTIC_ID,</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">        B.TREATMT_STRT_DT,</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
+          <t xml:space="preserve">        B.TREATMT_END_DT</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.CAPTR_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY A.CAPTR_DT DESC</t>
+          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr"/>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.CHNL_TYP_CD IN ('021','034')</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.SRC_DTA_STORE_CD IN ('139','140')</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>quit;</t>
+          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.CAPTR_DT &gt;= DATE '2025-01-01'</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>CAMPAIGN (IRI) — Summary (by year-month)</t>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY A.CAPTR_DT DESC</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>proc sql;</t>
-        </is>
-      </c>
+      <c r="A85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>%connectsql</t>
+          <t>);</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>select * from connection to teradata (</t>
+          <t>disconnect from teradata;</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SELECT</t>
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>quit;</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        EXTRACT(YEAR FROM A.CAPTR_DT)  AS yr,</t>
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>CAMPAIGN (IRI) — Summary (by year-month)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        EXTRACT(MONTH FROM A.CAPTR_DT) AS mo,</t>
+          <t>proc sql;</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)      AS unique_clients,</t>
+          <t>%connectsql</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        COUNT(DISTINCT A.EVNT_ID)      AS unique_transactions,</t>
+          <t>select * from connection to teradata (</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SUM(A.EVNT_AMT_CAD)            AS total_amt_cad</t>
-        </is>
-      </c>
+      <c r="A94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
+          <t xml:space="preserve">    SELECT</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
+          <t xml:space="preserve">        EXTRACT(YEAR FROM A.CAPTR_DT)  AS yr,</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
+          <t xml:space="preserve">        EXTRACT(MONTH FROM A.CAPTR_DT) AS mo,</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.CLNT_NO)      AS unique_clients,</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
+          <t xml:space="preserve">        COUNT(DISTINCT A.EVNT_ID)      AS unique_transactions,</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+          <t xml:space="preserve">        SUM(A.EVNT_AMT_CAD)            AS total_amt_cad</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      AND A.CAPTR_DT &gt;= DATE '2025-01-01'</t>
+          <t xml:space="preserve">    FROM DDWV01.EXT_CDS_CHNL_EVNT        AS A</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    GROUP BY 1, 2</t>
+          <t xml:space="preserve">    INNER JOIN DG6V01.TACTIC_EVNT_IP_AR_HIST AS B</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ORDER BY 1, 2</t>
+          <t xml:space="preserve">        ON A.CLNT_NO = B.CLNT_NO</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    WHERE A.ACTVY_TYP_CD = '031'</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>);</t>
+          <t xml:space="preserve">      AND A.CHNL_TYP_CD IN ('021','034')</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>disconnect from teradata;</t>
+          <t xml:space="preserve">      AND A.SRC_DTA_STORE_CD IN ('139','140')</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND SUBSTR(B.TACTIC_ID, 8, 3) = 'IRI'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.CAPTR_DT BETWEEN B.TREATMT_STRT_DT AND B.TREATMT_END_DT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      AND A.CAPTR_DT &gt;= DATE '2025-01-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUP BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ORDER BY 1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>);</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>disconnect from teradata;</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>quit;</t>
         </is>
